--- a/data/processed/tecnicos.xlsx
+++ b/data/processed/tecnicos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,27 +424,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>id_time</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>nome_tecnico</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>data_nascimento</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>nacionalidade</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>id_time</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>nome_time</t>
         </is>
       </c>
     </row>
@@ -452,27 +447,22 @@
       <c r="A2" t="n">
         <v>293</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="n">
+        <v>1765</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>Luis Zubeldía</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1981-01-13</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>13/01/1981</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Argentina</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1765</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Fluminense FC</t>
         </is>
       </c>
     </row>
@@ -480,27 +470,22 @@
       <c r="A3" t="n">
         <v>45858</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="n">
+        <v>1766</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Eduardo Domínguez</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1978-09-01</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>01/09/1978</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Argentina</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1766</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CA Mineiro</t>
         </is>
       </c>
     </row>
@@ -508,27 +493,22 @@
       <c r="A4" t="n">
         <v>293872</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" t="n">
+        <v>1767</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>Jéssica Lima</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1981-06-08</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1767</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Grêmio FBPA</t>
+          <t>08/06/1981</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Brazil</t>
         </is>
       </c>
     </row>
@@ -536,27 +516,22 @@
       <c r="A5" t="n">
         <v>278640</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" t="n">
+        <v>1768</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>João Eduardo Louro Baptista Cr</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1993-08-28</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>28/08/1993</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1768</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>CA Paranaense</t>
         </is>
       </c>
     </row>
@@ -564,27 +539,22 @@
       <c r="A6" t="n">
         <v>45403</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" t="n">
+        <v>1769</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Abel Ferreira</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1978-12-22</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>22/12/1978</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1769</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SE Palmeiras</t>
         </is>
       </c>
     </row>
@@ -592,27 +562,22 @@
       <c r="A7" t="n">
         <v>177226</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" t="n">
+        <v>1770</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Franclim Carvalho</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1987-03-30</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>30/03/1987</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1770</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Botafogo FR</t>
         </is>
       </c>
     </row>
@@ -620,27 +585,22 @@
       <c r="A8" t="n">
         <v>145312</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" t="n">
+        <v>1771</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>Artur Jorge</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1972-01-01</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>01/01/1972</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1771</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Cruzeiro EC</t>
         </is>
       </c>
     </row>
@@ -648,27 +608,22 @@
       <c r="A9" t="n">
         <v>248709</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" t="n">
+        <v>1772</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Fábio Matias</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1979-09-25</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1772</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Chapecoense AF</t>
+          <t>25/09/1979</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Brazil</t>
         </is>
       </c>
     </row>
@@ -676,27 +631,22 @@
       <c r="A10" t="n">
         <v>203358</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" t="n">
+        <v>1776</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Dorival Júnior</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1962-04-25</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>1776</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>São Paulo FC</t>
+          <t>25/04/1962</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Brazil</t>
         </is>
       </c>
     </row>
@@ -704,27 +654,22 @@
       <c r="A11" t="n">
         <v>12718</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" t="n">
+        <v>1777</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Rogério Ceni</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1973-01-22</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1777</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>EC Bahia</t>
+          <t>22/01/1973</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Brazil</t>
         </is>
       </c>
     </row>
@@ -732,27 +677,22 @@
       <c r="A12" t="n">
         <v>11165</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" t="n">
+        <v>1779</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Fernando Diniz</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1974-03-27</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1779</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SC Corinthians Paulista</t>
+          <t>27/03/1974</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Brazil</t>
         </is>
       </c>
     </row>
@@ -760,27 +700,22 @@
       <c r="A13" t="n">
         <v>293871</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" t="n">
+        <v>1780</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Possato</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1979-01-30</t>
-        </is>
-      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>1780</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>CR Vasco da Gama</t>
+          <t>30/01/1979</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Brazil</t>
         </is>
       </c>
     </row>
@@ -788,27 +723,22 @@
       <c r="A14" t="n">
         <v>213375</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" t="n">
+        <v>1782</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Jair Ventura</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1979-03-14</t>
-        </is>
-      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1782</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>EC Vitória</t>
+          <t>14/03/1979</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Brazil</t>
         </is>
       </c>
     </row>
@@ -816,27 +746,22 @@
       <c r="A15" t="n">
         <v>15925</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" t="n">
+        <v>1783</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Leonardo Jardim</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1974-08-01</t>
-        </is>
-      </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>01/08/1974</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1783</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>CR Flamengo</t>
         </is>
       </c>
     </row>
@@ -844,27 +769,22 @@
       <c r="A16" t="n">
         <v>246731</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" t="n">
+        <v>4241</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Fernando Seabra</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1977-06-19</t>
-        </is>
-      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>4241</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Coritiba FBC</t>
+          <t>19/06/1977</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Brazil</t>
         </is>
       </c>
     </row>
@@ -872,27 +792,22 @@
       <c r="A17" t="n">
         <v>11131</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" t="n">
+        <v>4286</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Vágner Mancini</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1966-10-24</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>4286</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>RB Bragantino</t>
+          <t>24/10/1966</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Brazil</t>
         </is>
       </c>
     </row>
@@ -900,27 +815,22 @@
       <c r="A18" t="n">
         <v>181493</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" t="n">
+        <v>4287</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Leo Condé</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1978-04-21</t>
-        </is>
-      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>4287</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Clube do Remo</t>
+          <t>21/04/1978</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Brazil</t>
         </is>
       </c>
     </row>
@@ -928,27 +838,22 @@
       <c r="A19" t="n">
         <v>249467</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" t="n">
+        <v>4364</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Rafael Guanaes</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1981-03-27</t>
-        </is>
-      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Mirassol FC</t>
+          <t>27/03/1981</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Brazil</t>
         </is>
       </c>
     </row>
@@ -956,27 +861,22 @@
       <c r="A20" t="n">
         <v>295217</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" t="n">
+        <v>6684</v>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Leonardo Ramos</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1987-05-18</t>
-        </is>
-      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>6684</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>SC Internacional</t>
+          <t>18/05/1987</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Brazil</t>
         </is>
       </c>
     </row>
@@ -984,27 +884,22 @@
       <c r="A21" t="n">
         <v>77180</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" t="n">
+        <v>6685</v>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>Cuca</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1963-06-07</t>
-        </is>
-      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>6685</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Santos FC</t>
+          <t>07/06/1963</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Brazil</t>
         </is>
       </c>
     </row>

--- a/data/processed/tecnicos.xlsx
+++ b/data/processed/tecnicos.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,12 +438,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>nacionalidade</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>data_nascimento</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>nacionalidade</t>
         </is>
       </c>
     </row>
@@ -457,13 +461,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13/01/1981</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
           <t>Argentina</t>
         </is>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>29599</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +482,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>01/09/1978</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
           <t>Argentina</t>
         </is>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>28734</v>
       </c>
     </row>
     <row r="4">
@@ -503,13 +503,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>08/06/1981</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>29745</v>
       </c>
     </row>
     <row r="5">
@@ -526,13 +524,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>28/08/1993</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
           <t>Portugal</t>
         </is>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>34209</v>
       </c>
     </row>
     <row r="6">
@@ -549,13 +545,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22/12/1978</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
           <t>Portugal</t>
         </is>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>28846</v>
       </c>
     </row>
     <row r="7">
@@ -572,13 +566,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>30/03/1987</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
           <t>Portugal</t>
         </is>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>31866</v>
       </c>
     </row>
     <row r="8">
@@ -595,13 +587,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>01/01/1972</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
           <t>Portugal</t>
         </is>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>26299</v>
       </c>
     </row>
     <row r="9">
@@ -618,13 +608,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>25/09/1979</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>29123</v>
       </c>
     </row>
     <row r="10">
@@ -641,13 +629,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>25/04/1962</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>22761</v>
       </c>
     </row>
     <row r="11">
@@ -664,13 +650,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>22/01/1973</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>26686</v>
       </c>
     </row>
     <row r="12">
@@ -687,13 +671,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>27/03/1974</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>27115</v>
       </c>
     </row>
     <row r="13">
@@ -710,13 +692,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>30/01/1979</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>28885</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +713,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>14/03/1979</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>28928</v>
       </c>
     </row>
     <row r="15">
@@ -756,13 +734,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>01/08/1974</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
           <t>Portugal</t>
         </is>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>27242</v>
       </c>
     </row>
     <row r="16">
@@ -779,13 +755,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19/06/1977</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>28295</v>
       </c>
     </row>
     <row r="17">
@@ -802,13 +776,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24/10/1966</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>24404</v>
       </c>
     </row>
     <row r="18">
@@ -825,13 +797,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>21/04/1978</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>28601</v>
       </c>
     </row>
     <row r="19">
@@ -848,13 +818,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>27/03/1981</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>29672</v>
       </c>
     </row>
     <row r="20">
@@ -871,13 +839,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>18/05/1987</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>31915</v>
       </c>
     </row>
     <row r="21">
@@ -894,13 +860,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>07/06/1963</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>23169</v>
       </c>
     </row>
   </sheetData>
